--- a/ResourcesPK/VehicleMasterModification.xlsx
+++ b/ResourcesPK/VehicleMasterModification.xlsx
@@ -141,9 +141,6 @@
     <t>50250327</t>
   </si>
   <si>
-    <t>781628746</t>
-  </si>
-  <si>
     <t>685124</t>
   </si>
   <si>
@@ -177,9 +174,6 @@
     <t>NMV</t>
   </si>
   <si>
-    <t>124x8217x240</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -199,6 +193,12 @@
   </si>
   <si>
     <t>0080</t>
+  </si>
+  <si>
+    <t>124,8217,2400</t>
+  </si>
+  <si>
+    <t>7816287465</t>
   </si>
 </sst>
 </file>
@@ -234,11 +234,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,68 +687,68 @@
         <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" t="s">
-        <v>51</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>42</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S2">
         <v>13</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y2">
         <v>1</v>
@@ -756,7 +757,7 @@
         <v>10</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB2">
         <v>10</v>
@@ -765,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="AD2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AE2">
         <v>10</v>

--- a/ResourcesPK/VehicleMasterModification.xlsx
+++ b/ResourcesPK/VehicleMasterModification.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
   <si>
     <t>Distributor Code*</t>
   </si>
@@ -199,12 +199,106 @@
   </si>
   <si>
     <t>7816287465</t>
+  </si>
+  <si>
+    <t>VehicleAB092</t>
+  </si>
+  <si>
+    <t>VehicleFA242</t>
+  </si>
+  <si>
+    <t>VehicleE09D2</t>
+  </si>
+  <si>
+    <t>VehicleD4785</t>
+  </si>
+  <si>
+    <t>Vehicle09F51</t>
+  </si>
+  <si>
+    <t>Vehicle22E0B</t>
+  </si>
+  <si>
+    <t>VehicleA3ED1</t>
+  </si>
+  <si>
+    <t>VehicleC41DF</t>
+  </si>
+  <si>
+    <t>VehicleACF86</t>
+  </si>
+  <si>
+    <t>Vehicle176CA</t>
+  </si>
+  <si>
+    <t>Vehicle337B0</t>
+  </si>
+  <si>
+    <t>Vehicle201DE</t>
+  </si>
+  <si>
+    <t>VehicleD2C66</t>
+  </si>
+  <si>
+    <t>Vehicle7B6AB</t>
+  </si>
+  <si>
+    <t>VehicleE10B1</t>
+  </si>
+  <si>
+    <t>Vehicle34295</t>
+  </si>
+  <si>
+    <t>Vehicle08887</t>
+  </si>
+  <si>
+    <t>Vehicle90D85</t>
+  </si>
+  <si>
+    <t>Vehicle9A8AF</t>
+  </si>
+  <si>
+    <t>Vehicle404F3</t>
+  </si>
+  <si>
+    <t>Vehicle83BCE</t>
+  </si>
+  <si>
+    <t>Vehicle545C8</t>
+  </si>
+  <si>
+    <t>Vehicle850AC</t>
+  </si>
+  <si>
+    <t>VehicleE6FB5</t>
+  </si>
+  <si>
+    <t>Vehicle1F6F6</t>
+  </si>
+  <si>
+    <t>VehicleDEB0A</t>
+  </si>
+  <si>
+    <t>VehicleAC68E</t>
+  </si>
+  <si>
+    <t>Vehicle71E7F</t>
+  </si>
+  <si>
+    <t>Vehicle5938E</t>
+  </si>
+  <si>
+    <t>Vehicle99C50</t>
+  </si>
+  <si>
+    <t>Vehicle8A121</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -523,44 +617,44 @@
   <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="79.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="36.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="47.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="31.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="43" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="45" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="16.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="12.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="8.26953125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="22.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="20.7265625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="15.26953125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.81640625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="45.81640625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.7265625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="9.54296875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="39.54296875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="16.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="79.81640625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="12.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="41.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="36.81640625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="18.26953125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="16.26953125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="47.26953125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.7265625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="31.1796875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.26953125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="12.26953125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="14.54296875"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="43.1796875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="43.7265625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="43.0"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="43.1796875"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="45.0"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="43.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.35">
@@ -573,13 +667,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -597,88 +691,88 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" t="s" s="0">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" t="s" s="0">
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" t="s" s="0">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" t="s" s="0">
         <v>38</v>
       </c>
     </row>
@@ -690,9 +784,9 @@
         <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -717,79 +811,79 @@
       <c r="L2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>50</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>41</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="0">
         <v>13</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>42</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>41</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>1</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="0">
         <v>10</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB2">
-        <v>10</v>
-      </c>
-      <c r="AC2">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AB2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AD2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="AE2">
-        <v>10</v>
-      </c>
-      <c r="AF2">
-        <v>10</v>
-      </c>
-      <c r="AG2">
-        <v>10</v>
-      </c>
-      <c r="AH2">
-        <v>10</v>
-      </c>
-      <c r="AI2">
-        <v>10</v>
-      </c>
-      <c r="AJ2">
-        <v>10</v>
-      </c>
-      <c r="AK2">
-        <v>10</v>
-      </c>
-      <c r="AM2">
+      <c r="AE2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AG2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AH2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AK2" s="0">
+        <v>10</v>
+      </c>
+      <c r="AM2" s="0">
         <v>10</v>
       </c>
     </row>
